--- a/wildlife/reports/United-Kingdom/abundance/Abingdon/Butterflies/abundance.xlsx
+++ b/wildlife/reports/United-Kingdom/abundance/Abingdon/Butterflies/abundance.xlsx
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
@@ -583,10 +583,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D10" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11">
@@ -647,10 +647,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15">
